--- a/vorpruefung_output.xlsx
+++ b/vorpruefung_output.xlsx
@@ -19068,16 +19068,28 @@
         <v>227</v>
       </c>
       <c r="C2" t="str">
-        <f t="array" ref="C2">_xlfn.LET(v, _xlfn.VSTACK('III. Finanzberichte'!$B$41:$F$45,'III. Finanzberichte'!$I$41:$M$45,'III. Finanzberichte'!$P$41:$T$45,'III. Finanzberichte'!$W$41:$AA$45,'III. Finanzberichte'!$AD$41:$AH$45,'III. Finanzberichte'!$AK$41:$AO$45,'III. Finanzberichte'!$AR$41:$AV$45,'III. Finanzberichte'!$AY$41:$BC$45,'III. Finanzberichte'!$BF$41:$BJ$45,'III. Finanzberichte'!$BM$41:$BQ$45,'III. Finanzberichte'!$BT$41:$BX$45,'III. Finanzberichte'!$CA$41:$CE$45,'III. Finanzberichte'!$CH$41:$CL$45,'III. Finanzberichte'!$CO$41:$CS$45,'III. Finanzberichte'!$CV$41:$CZ$45,'III. Finanzberichte'!$DC$41:$DG$45,'III. Finanzberichte'!$DJ$41:$DN$45,'III. Finanzberichte'!$DQ$41:$DU$45), _xlfn.FILTER(v, (INDEX(v,0,3)&lt;&gt;0)+(INDEX(v,0,4)&lt;&gt;0), ""))</f>
+        <f>_xlfn.FILTER(AA2#, (_xlfn.CHOOSECOLS(AA2#,3)&lt;&gt;0)+(_xlfn.CHOOSECOLS(AA2#,4)&lt;&gt;0), "")</f>
       </c>
       <c r="I2" t="str">
-        <f t="array" ref="I2">_xlfn.LET(v, _xlfn.VSTACK('III. Finanzberichte'!$B$50:$F$55,'III. Finanzberichte'!$I$50:$M$55,'III. Finanzberichte'!$P$50:$T$55,'III. Finanzberichte'!$W$50:$AA$55,'III. Finanzberichte'!$AD$50:$AH$55,'III. Finanzberichte'!$AK$50:$AO$55,'III. Finanzberichte'!$AR$50:$AV$55,'III. Finanzberichte'!$AY$50:$BC$55,'III. Finanzberichte'!$BF$50:$BJ$55,'III. Finanzberichte'!$BM$50:$BQ$55,'III. Finanzberichte'!$BT$50:$BX$55,'III. Finanzberichte'!$CA$50:$CE$55,'III. Finanzberichte'!$CH$50:$CL$55,'III. Finanzberichte'!$CO$50:$CS$55,'III. Finanzberichte'!$CV$50:$CZ$55,'III. Finanzberichte'!$DC$50:$DG$55,'III. Finanzberichte'!$DJ$50:$DN$55,'III. Finanzberichte'!$DQ$50:$DU$55), _xlfn.FILTER(v, (INDEX(v,0,3)&lt;&gt;0)+(INDEX(v,0,4)&lt;&gt;0), ""))</f>
+        <f>_xlfn.FILTER(AG2#, (_xlfn.CHOOSECOLS(AG2#,3)&lt;&gt;0)+(_xlfn.CHOOSECOLS(AG2#,4)&lt;&gt;0), "")</f>
       </c>
       <c r="O2" t="str">
-        <f t="array" ref="O2">_xlfn.LET(v, _xlfn.VSTACK('III. Finanzberichte'!$B$19:$F$26,'III. Finanzberichte'!$I$19:$M$26,'III. Finanzberichte'!$P$19:$T$26,'III. Finanzberichte'!$W$19:$AA$26,'III. Finanzberichte'!$AD$19:$AH$26,'III. Finanzberichte'!$AK$19:$AO$26,'III. Finanzberichte'!$AR$19:$AV$26,'III. Finanzberichte'!$AY$19:$BC$26,'III. Finanzberichte'!$BF$19:$BJ$26,'III. Finanzberichte'!$BM$19:$BQ$26,'III. Finanzberichte'!$BT$19:$BX$26,'III. Finanzberichte'!$CA$19:$CE$26,'III. Finanzberichte'!$CH$19:$CL$26,'III. Finanzberichte'!$CO$19:$CS$26,'III. Finanzberichte'!$CV$19:$CZ$26,'III. Finanzberichte'!$DC$19:$DG$26,'III. Finanzberichte'!$DJ$19:$DN$26,'III. Finanzberichte'!$DQ$19:$DU$26), _xlfn.FILTER(v, (INDEX(v,0,2)&lt;&gt;0)+(INDEX(v,0,3)&lt;&gt;0), ""))</f>
+        <f>_xlfn.FILTER(AM2#, (_xlfn.CHOOSECOLS(AM2#,2)&lt;&gt;0)+(_xlfn.CHOOSECOLS(AM2#,3)&lt;&gt;0), "")</f>
       </c>
       <c r="U2" t="str">
-        <f t="array" ref="U2">_xlfn.LET(v, _xlfn.VSTACK('IV. MA'!$B$10:$D$17,'IV. MA'!$F$10:$H$17,'IV. MA'!$J$10:$L$17,'IV. MA'!$N$10:$P$17,'IV. MA'!$R$10:$T$17,'IV. MA'!$V$10:$X$17,'IV. MA'!$Z$10:$AB$17,'IV. MA'!$AD$10:$AF$17,'IV. MA'!$AH$10:$AJ$17,'IV. MA'!$AL$10:$AN$17,'IV. MA'!$AP$10:$AR$17,'IV. MA'!$AT$10:$AV$17,'IV. MA'!$AX$10:$AZ$17,'IV. MA'!$BB$10:$BD$17,'IV. MA'!$BF$10:$BH$17,'IV. MA'!$BJ$10:$BL$17,'IV. MA'!$BN$10:$BP$17,'IV. MA'!$BR$10:$BT$17), _xlfn.FILTER(v, (INDEX(v,0,2)&lt;&gt;0)+(INDEX(v,0,3)&lt;&gt;0), ""))</f>
+        <f>_xlfn.FILTER(AS2#, (_xlfn.CHOOSECOLS(AS2#,2)&lt;&gt;0)+(_xlfn.CHOOSECOLS(AS2#,3)&lt;&gt;0), "")</f>
+      </c>
+      <c r="AA2" t="str">
+        <f>_xlfn.VSTACK('III. Finanzberichte'!$B$41:$F$45,'III. Finanzberichte'!$I$41:$M$45,'III. Finanzberichte'!$P$41:$T$45,'III. Finanzberichte'!$W$41:$AA$45,'III. Finanzberichte'!$AD$41:$AH$45,'III. Finanzberichte'!$AK$41:$AO$45,'III. Finanzberichte'!$AR$41:$AV$45,'III. Finanzberichte'!$AY$41:$BC$45,'III. Finanzberichte'!$BF$41:$BJ$45,'III. Finanzberichte'!$BM$41:$BQ$45,'III. Finanzberichte'!$BT$41:$BX$45,'III. Finanzberichte'!$CA$41:$CE$45,'III. Finanzberichte'!$CH$41:$CL$45,'III. Finanzberichte'!$CO$41:$CS$45,'III. Finanzberichte'!$CV$41:$CZ$45,'III. Finanzberichte'!$DC$41:$DG$45,'III. Finanzberichte'!$DJ$41:$DN$45,'III. Finanzberichte'!$DQ$41:$DU$45)</f>
+      </c>
+      <c r="AG2" t="str">
+        <f>_xlfn.VSTACK('III. Finanzberichte'!$B$50:$F$55,'III. Finanzberichte'!$I$50:$M$55,'III. Finanzberichte'!$P$50:$T$55,'III. Finanzberichte'!$W$50:$AA$55,'III. Finanzberichte'!$AD$50:$AH$55,'III. Finanzberichte'!$AK$50:$AO$55,'III. Finanzberichte'!$AR$50:$AV$55,'III. Finanzberichte'!$AY$50:$BC$55,'III. Finanzberichte'!$BF$50:$BJ$55,'III. Finanzberichte'!$BM$50:$BQ$55,'III. Finanzberichte'!$BT$50:$BX$55,'III. Finanzberichte'!$CA$50:$CE$55,'III. Finanzberichte'!$CH$50:$CL$55,'III. Finanzberichte'!$CO$50:$CS$55,'III. Finanzberichte'!$CV$50:$CZ$55,'III. Finanzberichte'!$DC$50:$DG$55,'III. Finanzberichte'!$DJ$50:$DN$55,'III. Finanzberichte'!$DQ$50:$DU$55)</f>
+      </c>
+      <c r="AM2" t="str">
+        <f>_xlfn.VSTACK('III. Finanzberichte'!$B$19:$F$26,'III. Finanzberichte'!$I$19:$M$26,'III. Finanzberichte'!$P$19:$T$26,'III. Finanzberichte'!$W$19:$AA$26,'III. Finanzberichte'!$AD$19:$AH$26,'III. Finanzberichte'!$AK$19:$AO$26,'III. Finanzberichte'!$AR$19:$AV$26,'III. Finanzberichte'!$AY$19:$BC$26,'III. Finanzberichte'!$BF$19:$BJ$26,'III. Finanzberichte'!$BM$19:$BQ$26,'III. Finanzberichte'!$BT$19:$BX$26,'III. Finanzberichte'!$CA$19:$CE$26,'III. Finanzberichte'!$CH$19:$CL$26,'III. Finanzberichte'!$CO$19:$CS$26,'III. Finanzberichte'!$CV$19:$CZ$26,'III. Finanzberichte'!$DC$19:$DG$26,'III. Finanzberichte'!$DJ$19:$DN$26,'III. Finanzberichte'!$DQ$19:$DU$26)</f>
+      </c>
+      <c r="AS2" t="str">
+        <f>_xlfn.VSTACK('IV. MA'!$B$10:$D$17,'IV. MA'!$F$10:$H$17,'IV. MA'!$J$10:$L$17,'IV. MA'!$N$10:$P$17,'IV. MA'!$R$10:$T$17,'IV. MA'!$V$10:$X$17,'IV. MA'!$Z$10:$AB$17,'IV. MA'!$AD$10:$AF$17,'IV. MA'!$AH$10:$AJ$17,'IV. MA'!$AL$10:$AN$17,'IV. MA'!$AP$10:$AR$17,'IV. MA'!$AT$10:$AV$17,'IV. MA'!$AX$10:$AZ$17,'IV. MA'!$BB$10:$BD$17,'IV. MA'!$BF$10:$BH$17,'IV. MA'!$BJ$10:$BL$17,'IV. MA'!$BN$10:$BP$17,'IV. MA'!$BR$10:$BT$17)</f>
       </c>
     </row>
     <row r="3">
